--- a/ig/DM-SEPTEMBRE-2025/CodeSystem-TRE-R356-ProfessionRessource.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/CodeSystem-TRE-R356-ProfessionRessource.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="256">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250710120000</t>
+    <t>20250918120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-10T12:00:00+01:00</t>
+    <t>2025-09-18T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -773,6 +773,9 @@
   </si>
   <si>
     <t>Psychologue du travail</t>
+  </si>
+  <si>
+    <t>Professionnel de psychologie intervenant en santé au travail pour préserver la santé mentale des salariés et améliorer les conditions de travail, au travers de diagnostics, conseils, évaluation des risques psychosociaux et accompagnement des actions collectives ou individuelles, en lien avec le médecin du travail.</t>
   </si>
   <si>
     <t>131</t>
@@ -2379,17 +2382,19 @@
       <c r="C99" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="D99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>253</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
         <v>58</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D100" s="2"/>
     </row>
